--- a/artfynd/A 63179-2025 artfynd.xlsx
+++ b/artfynd/A 63179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116257115</v>
+        <v>127708714</v>
       </c>
       <c r="B2" t="n">
-        <v>90435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417576</v>
+        <v>417527</v>
       </c>
       <c r="R2" t="n">
-        <v>7047933</v>
+        <v>7048065</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,62 +789,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116257094</v>
+        <v>127708677</v>
       </c>
       <c r="B3" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417477</v>
+        <v>417526</v>
       </c>
       <c r="R3" t="n">
-        <v>7048227</v>
+        <v>7048033</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +875,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,62 +910,71 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116257092</v>
+        <v>127708732</v>
       </c>
       <c r="B4" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417492</v>
+        <v>417527</v>
       </c>
       <c r="R4" t="n">
-        <v>7048275</v>
+        <v>7048065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +1001,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,27 +1036,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116257067</v>
+        <v>127698127</v>
       </c>
       <c r="B5" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1059,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>417604</v>
+        <v>417655</v>
       </c>
       <c r="R5" t="n">
-        <v>7048024</v>
+        <v>7047971</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,17 +1113,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,27 +1143,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116257065</v>
+        <v>127708795</v>
       </c>
       <c r="B6" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1166,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417638</v>
+        <v>417421</v>
       </c>
       <c r="R6" t="n">
-        <v>7047950</v>
+        <v>7048253</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,17 +1220,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,65 +1255,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116257108</v>
+        <v>127698142</v>
       </c>
       <c r="B7" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417696</v>
+        <v>417655</v>
       </c>
       <c r="R7" t="n">
-        <v>7047991</v>
+        <v>7047971</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,17 +1332,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,27 +1362,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116257084</v>
+        <v>127698214</v>
       </c>
       <c r="B8" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,37 +1385,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417472</v>
+        <v>417632</v>
       </c>
       <c r="R8" t="n">
-        <v>7048321</v>
+        <v>7047966</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,17 +1439,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,62 +1469,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116257075</v>
+        <v>127708763</v>
       </c>
       <c r="B9" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417510</v>
+        <v>417421</v>
       </c>
       <c r="R9" t="n">
-        <v>7048076</v>
+        <v>7048253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,17 +1546,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,59 +1576,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116257093</v>
+        <v>127708822</v>
       </c>
       <c r="B10" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kall NNÖ, Jmt</t>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>417473</v>
+        <v>417421</v>
       </c>
       <c r="R10" t="n">
         <v>7048253</v>
@@ -1596,17 +1653,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På bark på stam av levande gammal sälg i kanten av gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,12 +1688,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1636,12 +1703,7 @@
         <v>116257056</v>
       </c>
       <c r="B11" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,15 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116257070</v>
+        <v>116257058</v>
       </c>
       <c r="B12" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>417588</v>
+        <v>417666</v>
       </c>
       <c r="R12" t="n">
-        <v>7048008</v>
+        <v>7047956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116257068</v>
+        <v>116257060</v>
       </c>
       <c r="B13" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>417574</v>
+        <v>417655</v>
       </c>
       <c r="R13" t="n">
-        <v>7048022</v>
+        <v>7047942</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1979,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,15 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116257107</v>
+        <v>116257061</v>
       </c>
       <c r="B14" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>417645</v>
+        <v>417653</v>
       </c>
       <c r="R14" t="n">
-        <v>7048051</v>
+        <v>7047944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2081,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,15 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116257064</v>
+        <v>116257063</v>
       </c>
       <c r="B15" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>417640</v>
+        <v>417643</v>
       </c>
       <c r="R15" t="n">
-        <v>7047949</v>
+        <v>7047947</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,15 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116257095</v>
+        <v>116257064</v>
       </c>
       <c r="B16" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>417489</v>
+        <v>417640</v>
       </c>
       <c r="R16" t="n">
-        <v>7048197</v>
+        <v>7047949</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,15 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116257069</v>
+        <v>116257065</v>
       </c>
       <c r="B17" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>417586</v>
+        <v>417638</v>
       </c>
       <c r="R17" t="n">
-        <v>7048005</v>
+        <v>7047950</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,15 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116257105</v>
+        <v>116257066</v>
       </c>
       <c r="B18" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>417623</v>
+        <v>417651</v>
       </c>
       <c r="R18" t="n">
-        <v>7048084</v>
+        <v>7047957</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,15 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116257078</v>
+        <v>116257067</v>
       </c>
       <c r="B19" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>417483</v>
+        <v>417604</v>
       </c>
       <c r="R19" t="n">
-        <v>7048105</v>
+        <v>7048024</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,15 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>116257102</v>
+        <v>116257068</v>
       </c>
       <c r="B20" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>417578</v>
+        <v>417574</v>
       </c>
       <c r="R20" t="n">
-        <v>7048083</v>
+        <v>7048022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2693,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,15 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116257090</v>
+        <v>116257069</v>
       </c>
       <c r="B21" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>417484</v>
+        <v>417586</v>
       </c>
       <c r="R21" t="n">
-        <v>7048292</v>
+        <v>7048005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,15 +2822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116257079</v>
+        <v>116257070</v>
       </c>
       <c r="B22" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2857,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>417474</v>
+        <v>417588</v>
       </c>
       <c r="R22" t="n">
-        <v>7048132</v>
+        <v>7048008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2897,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,15 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116257058</v>
+        <v>116257071</v>
       </c>
       <c r="B23" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2959,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>417666</v>
+        <v>417575</v>
       </c>
       <c r="R23" t="n">
-        <v>7047956</v>
+        <v>7047911</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2999,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,15 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116257074</v>
+        <v>116257072</v>
       </c>
       <c r="B24" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>417502</v>
+        <v>417507</v>
       </c>
       <c r="R24" t="n">
-        <v>7048054</v>
+        <v>7047914</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3101,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,15 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116257080</v>
+        <v>116257074</v>
       </c>
       <c r="B25" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>417468</v>
+        <v>417502</v>
       </c>
       <c r="R25" t="n">
-        <v>7048158</v>
+        <v>7048054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,15 +3230,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116257106</v>
+        <v>116257075</v>
       </c>
       <c r="B26" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>417631</v>
+        <v>417510</v>
       </c>
       <c r="R26" t="n">
-        <v>7048036</v>
+        <v>7048076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3305,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,15 +3332,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116257063</v>
+        <v>116257076</v>
       </c>
       <c r="B27" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>417643</v>
+        <v>417492</v>
       </c>
       <c r="R27" t="n">
-        <v>7047947</v>
+        <v>7048076</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,15 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116257076</v>
+        <v>116257078</v>
       </c>
       <c r="B28" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3492,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>417492</v>
+        <v>417483</v>
       </c>
       <c r="R28" t="n">
-        <v>7048076</v>
+        <v>7048105</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,15 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116257082</v>
+        <v>116257079</v>
       </c>
       <c r="B29" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>417423</v>
+        <v>417474</v>
       </c>
       <c r="R29" t="n">
-        <v>7048302</v>
+        <v>7048132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,15 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116257072</v>
+        <v>116257080</v>
       </c>
       <c r="B30" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>417507</v>
+        <v>417468</v>
       </c>
       <c r="R30" t="n">
-        <v>7047914</v>
+        <v>7048158</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3713,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,15 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116257066</v>
+        <v>116257081</v>
       </c>
       <c r="B31" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3813,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>417651</v>
+        <v>417428</v>
       </c>
       <c r="R31" t="n">
-        <v>7047957</v>
+        <v>7048258</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3815,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,15 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116257081</v>
+        <v>116257082</v>
       </c>
       <c r="B32" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>417428</v>
+        <v>417423</v>
       </c>
       <c r="R32" t="n">
-        <v>7048258</v>
+        <v>7048302</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3917,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3990,12 +3947,7 @@
         <v>116257083</v>
       </c>
       <c r="B33" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4094,15 +4046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116257071</v>
+        <v>116257084</v>
       </c>
       <c r="B34" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4134,10 +4081,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>417575</v>
+        <v>417472</v>
       </c>
       <c r="R34" t="n">
-        <v>7047911</v>
+        <v>7048321</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4201,15 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116257060</v>
+        <v>116257085</v>
       </c>
       <c r="B35" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4241,10 +4183,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>417655</v>
+        <v>417511</v>
       </c>
       <c r="R35" t="n">
-        <v>7047942</v>
+        <v>7048311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4311,12 +4253,7 @@
         <v>116257088</v>
       </c>
       <c r="B36" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4415,15 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116257061</v>
+        <v>116257089</v>
       </c>
       <c r="B37" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4455,10 +4387,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>417653</v>
+        <v>417499</v>
       </c>
       <c r="R37" t="n">
-        <v>7047944</v>
+        <v>7048292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4427,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4522,15 +4454,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116257096</v>
+        <v>116257090</v>
       </c>
       <c r="B38" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,10 +4489,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>417486</v>
+        <v>417484</v>
       </c>
       <c r="R38" t="n">
-        <v>7048152</v>
+        <v>7048292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4629,15 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116257089</v>
+        <v>116257091</v>
       </c>
       <c r="B39" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4669,10 +4591,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>417499</v>
+        <v>417487</v>
       </c>
       <c r="R39" t="n">
-        <v>7048292</v>
+        <v>7048285</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4631,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4736,15 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>116257091</v>
+        <v>116257092</v>
       </c>
       <c r="B40" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,10 +4693,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>417487</v>
+        <v>417492</v>
       </c>
       <c r="R40" t="n">
-        <v>7048285</v>
+        <v>7048275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4733,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4843,15 +4760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>116257104</v>
+        <v>116257093</v>
       </c>
       <c r="B41" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,10 +4795,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>417583</v>
+        <v>417473</v>
       </c>
       <c r="R41" t="n">
-        <v>7048094</v>
+        <v>7048253</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4835,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4950,15 +4862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>116257099</v>
+        <v>116257094</v>
       </c>
       <c r="B42" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4990,10 +4897,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>417604</v>
+        <v>417477</v>
       </c>
       <c r="R42" t="n">
-        <v>7048185</v>
+        <v>7048227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,15 +4964,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116257097</v>
+        <v>116257095</v>
       </c>
       <c r="B43" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5097,10 +4999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>417560</v>
+        <v>417489</v>
       </c>
       <c r="R43" t="n">
-        <v>7048078</v>
+        <v>7048197</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5164,15 +5066,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116257085</v>
+        <v>116257096</v>
       </c>
       <c r="B44" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,10 +5101,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>417511</v>
+        <v>417486</v>
       </c>
       <c r="R44" t="n">
-        <v>7048311</v>
+        <v>7048152</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5271,10 +5168,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127698127</v>
+        <v>116257097</v>
       </c>
       <c r="B45" t="n">
-        <v>82884</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5282,37 +5179,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>417655</v>
+        <v>417560</v>
       </c>
       <c r="R45" t="n">
-        <v>7047971</v>
+        <v>7048078</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5336,22 +5233,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5366,71 +5258,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127708732</v>
+        <v>116257099</v>
       </c>
       <c r="B46" t="n">
-        <v>79202</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>417527</v>
+        <v>417604</v>
       </c>
       <c r="R46" t="n">
-        <v>7048065</v>
+        <v>7048185</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5457,27 +5335,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gren på gammal levande gran i gammal granskog</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5492,22 +5360,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127698142</v>
+        <v>116257102</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,37 +5383,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>417655</v>
+        <v>417578</v>
       </c>
       <c r="R47" t="n">
-        <v>7047971</v>
+        <v>7048083</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5569,22 +5437,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5599,22 +5462,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127698214</v>
+        <v>116257104</v>
       </c>
       <c r="B48" t="n">
-        <v>75167</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5622,37 +5485,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>417632</v>
+        <v>417583</v>
       </c>
       <c r="R48" t="n">
-        <v>7047966</v>
+        <v>7048094</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5676,22 +5539,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5706,22 +5564,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127698200</v>
+        <v>116257105</v>
       </c>
       <c r="B49" t="n">
-        <v>78026</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5729,37 +5587,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>417655</v>
+        <v>417623</v>
       </c>
       <c r="R49" t="n">
-        <v>7047970</v>
+        <v>7048084</v>
       </c>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5783,22 +5641,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5813,22 +5666,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127708714</v>
+        <v>116257106</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5836,48 +5689,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+          <t>Kall NNÖ, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>417527</v>
+        <v>417631</v>
       </c>
       <c r="R50" t="n">
-        <v>7048065</v>
+        <v>7048036</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,27 +5743,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,15 +5768,427 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>116257107</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kall NNÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>417645</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7048051</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>116257108</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kall NNÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>417696</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7047991</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>89584852</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Dalbyssjet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>417591</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7047991</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127698200</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stor-Dalbyssjet, Stor-Dalbyssjet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>417655</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7047970</v>
+      </c>
+      <c r="S54" t="n">
+        <v>13</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson, August Nordin</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63179-2025 artfynd.xlsx
+++ b/artfynd/A 63179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127708714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127708677</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127708732</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127708795</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1371,6 +1401,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698142</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698214</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1585,6 +1625,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127708763</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127708822</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257056</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1901,6 +1956,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257058</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2003,6 +2063,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257060</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257061</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2207,6 +2277,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257063</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2309,6 +2384,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257064</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2411,6 +2491,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257065</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2513,6 +2598,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257066</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257067</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2717,6 +2812,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257068</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2819,6 +2919,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257069</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2921,6 +3026,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257070</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3023,6 +3133,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257071</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3125,6 +3240,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257072</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3227,6 +3347,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257074</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3329,6 +3454,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257075</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3431,6 +3561,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257076</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3533,6 +3668,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257078</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3635,6 +3775,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257079</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3737,6 +3882,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257080</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3839,6 +3989,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257081</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3941,6 +4096,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257082</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4043,6 +4203,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257083</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4145,6 +4310,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257084</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4247,6 +4417,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257085</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4349,6 +4524,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257088</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4451,6 +4631,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257089</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4553,6 +4738,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257090</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4655,6 +4845,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257091</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4757,6 +4952,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257092</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4859,6 +5059,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257093</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4961,6 +5166,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257094</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5063,6 +5273,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257095</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5165,6 +5380,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257096</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5267,6 +5487,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257097</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5369,6 +5594,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257099</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5471,6 +5701,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257102</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5573,6 +5808,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257104</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5675,6 +5915,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257105</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5777,6 +6022,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257106</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5879,6 +6129,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257107</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5981,6 +6236,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116257108</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6082,6 +6342,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584852</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6189,8 +6454,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>